--- a/5_Snowballing/Backward_Snowballing_1.xlsx
+++ b/5_Snowballing/Backward_Snowballing_1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antoniotrovato/Documents/GitHub/RegressionTestingOptimizationSLR/5_Snowballing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA1BFF9-6597-154A-A5A9-E0DCD270C7AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A49B7A7-B5A9-C546-87C3-EDDEE3A7E941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="284">
   <si>
     <t>ID</t>
   </si>
@@ -153,15 +153,6 @@
   </si>
   <si>
     <t>Type</t>
-  </si>
-  <si>
-    <t>Relation-based test case prioritization for regression testing</t>
-  </si>
-  <si>
-    <t>The importance of using requirements information in the testing phase has been well recognized by the requirements engineering community, but to date, a vast majority of regression testing techniques have primarily relied on software code information. Incorporating requirements information into the current testing practice could help software engineers identify the source of defects more easily, validate the product against requirements, and maintain software products in a holistic way. In this paper, we investigate whether the requirements-based clustering approach that incorporates traditional code analysis information can improve the effectiveness of test case prioritization techniques. To investigate the effectiveness of our approach, we performed an empirical study using two Java programs with multiple versions and requirements documents. Our results indicate that the use of requirements information during the test case prioritization process can be beneficial.</t>
-  </si>
-  <si>
-    <t>Testing is the process of evaluating a system by manual or automated means. While Regression Test Selection (RTS) discards test cases and Test Suite Minimization (TSM) shows diminution in fault detection rate, Test Case Prioritization (TCP) does not discard test cases. Test Case Prioritization techniques can be coverage or historical information based or model based. It can also be cost-time aware or requirement-risk aware. GUI/Web applications need special prioritization mechanism. In this paper, 90 scholarly articles ranging from 2001 to 2018 have been reviewed. We have explored IEEE, Wiley, ACM Library, Springer, Taylor &amp; Francis and Elsevier database. We have also described each prioritization method with their findings and subject programs. This paper includes a chronological catalogue listing of the reviewed papers. We have framed three research questions which sum up the frequently used prioritization metrics, regularly used subject programs and the distribution of different prioritization techniques. To the best of our knowledge, this is the first review with a detail report of the last 18 years of TCP techniques. We hope this article will be beneficial for both beginners and seasoned professionals.</t>
   </si>
   <si>
     <t>Journal of Systems and Software</t>
@@ -271,15 +262,6 @@
   </si>
   <si>
     <t>Test-case prioritization, proposed at the end of last century, aims to schedule the execution order of test cases so as to improve test effectiveness. In the past years, test-case prioritization has gained much attention, and has significant achievements in five aspects: prioritization algorithms, coverage criteria, measurement, practical concerns involved, and application scenarios. In this article, we will first review the achievements of test-case prioritization from these five aspects and then give our perspectives on its challenges.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> A survey on different approaches for software test case prioritization</t>
-  </si>
-  <si>
-    <t>R Mukherjee, KS Patnaik</t>
-  </si>
-  <si>
-    <t>Journal of King Saud University-Computer and Information Sciences, 2021</t>
   </si>
   <si>
     <t>A systematic literature study of regression test case prioritization approaches</t>
@@ -327,12 +309,6 @@
     <t>Information and Software Technology, 2019</t>
   </si>
   <si>
-    <t>Test case prioritization using requirements-based clustering</t>
-  </si>
-  <si>
-    <t>MJ Arafeen, H Do</t>
-  </si>
-  <si>
     <t>Comparing white-box and black-box test prioritization</t>
   </si>
   <si>
@@ -382,19 +358,6 @@
 Regression test case selection techniques attempt to increase the testing effectiveness based on the measurement capabilities, such as cost, coverage, and fault detection. This systematic literature review presents state-of-the-art research in effective regression test case selection techniques. We examined 47 empirical studies published between 2007 and 2015. The selected studies are categorized according to the selection procedure, empirical study design, and adequacy criteria with respect to their effectiveness measurement capability and methods used to measure the validity of these results.
 The results showed that mining and learning-based regression test case selection was reported in 39% of the studies, unit level testing was reported in 18% of the studies, and object-oriented environment (Java) was used in 26% of the studies. Structural faults, the most common target, was used in 55% of the studies. Overall, only 39% of the studies conducted followed experimental guidelines and are reproducible.
 There are 7 different cost measures, 13 different coverage types, and 5 fault-detection metrics reported in these studies. It is also observed that 70% of the studies being analyzed used cost as the effectiveness measure compared to 31% that used fault-detection capability and 16% that used coverage.</t>
-  </si>
-  <si>
-    <t>An effective approach for regression test case selection using pareto based multi-objective harmony search</t>
-  </si>
-  <si>
-    <t>A Choudhary, AP Agrawal, A Kaur</t>
-  </si>
-  <si>
-    <t>Proceedings of the 11th International Workshop on Search-Based Software Testing, 2018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Regression testing is a way of catching bugs in new builds and releases to avoid the product risks. Corrective, progressive, retest all and selective regression testing are strategies to perform regression testing. Retesting all existing test cases is one of the most reliable approaches but it is costly in terms of time and effort. This limitation opened a scope to optimize regression testing cost by selecting only a subset of test cases that can detect faults in optimal time and effort. This paper proposes Pareto based Multi-Objective Harmony Search approach for regression test case selection from an existing test suite to achieve some test adequacy criteria. Fault coverage, unique faults covered and algorithm execution time are utilised as performance measures to achieve optimization criteria. The performance evaluation of proposed approach is performed against Bat Search and Cuckoo Search optimization. The results of statistical tests indicate significant improvement over existing approaches.</t>
   </si>
   <si>
     <t>Regression test case selection and prioritization for object oriented software</t>
@@ -531,30 +494,6 @@
   </si>
   <si>
     <t>Modified source code validation is done by regression testing. In regression testing, the time and resources are limited, in which we have to select the minimal test cases from test suites to reduce execution time. The test case minimization process deals with the optimization of the regression testing by removing redundant test cases or prioritizing the test cases. This study proposed a test case prioritization approach based on multiobjective particle swarm optimization (MOPSO) by considering minimum execution time, maximum fault detection ability, and maximum code coverage. The MOPSO algorithm is used for the prioritization of test cases with parameters including execution time, fault detection ability, and code coverage. Three datasets are selected to evaluate the proposed MOPSO technique including TreeDataStructure, JodaTime, and Triangle. The proposed MOPSO is compared with the no ordering, reverse ordering, and random ordering technique for evaluating the effectiveness. The higher values of results represent the more effectiveness and the efficiency of the proposed MOPSO as compared to other approaches for TreeDataStructure, JodaTime, and Triangle datasets. The result is presented to 100‐index mode relevant from low to high values; after that, test cases are prioritized. The experiment is conducted on three open‐source java applications and evaluated using metrics inclusiveness, precision, and size reduction of a matrix of the test suite. The results revealed that all scenarios performed well in acceptable mode, and the technique is 17% to 86% more effective in terms of inclusiveness, 33% to 85% more effective in terms of precision, and 17% minimum to 86% maximum in size reduction of metrics.</t>
-  </si>
-  <si>
-    <t>Jianlei Chia, Yu Quc, Qinghua Zhenga, Zijiang Yangb, Wuxia Jina, Di Cuia, Ting Liua</t>
-  </si>
-  <si>
-    <t>Test case prioritization (TCP), which aims at detecting faults as early as possible is broadly used in pro-
-gram regression testing. Most existing TCP techniques exploit coverage information with the hypothesis
-that higher coverage has more chance to catch bugs. Static structure information such as function and
-statement are frequently employed as coverage granularity. However, the former consumes less costs but
-presents lower capability to detect faults, the latter typically incurs more overhead.
-In this paper, dynamic function call sequences are argued that can guide TCP effectively. Same set of func-
-tions/statements can exhibit very different execution behaviors. Therefore, mapping program behaviors
-to unit-based (function/statement) coverage may not be enough to predict fault detection capability. We
-propose a new approach AGC (Additional Greedy method Call sequence). Our approach leverages dynamic
-relation-based coverage as measurement to extend the original additional greedy coverage algorithm in
-TCP techniques.
-We conduct our experiments on eight real-world java open source projects and systematically compare
-AGC against 22 state-of-the-art TCP techniques with different granularities. Results show that AGC out-
-performs existing techniques on large programs in terms of bug detection capability, and also achieves
-the highest mean APFD value. The performance demonstrates a growth trend as the size of the program
-increases.</t>
-  </si>
-  <si>
-    <t>The Journal of Systems and Software</t>
   </si>
   <si>
     <t>Multi-objective regression test selection in practice: An empirical study in the defense software industry</t>
@@ -1355,7 +1294,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AN67"/>
+  <dimension ref="A1:AN63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.2">
@@ -1482,242 +1421,242 @@
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F2">
         <v>2016</v>
       </c>
       <c r="J2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="AN2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" t="s">
         <v>51</v>
       </c>
-      <c r="D3" t="s">
-        <v>54</v>
-      </c>
       <c r="E3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F3">
         <v>2018</v>
       </c>
       <c r="J3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AN3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F4">
         <v>2017</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="AN4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F5">
         <v>2017</v>
       </c>
       <c r="J5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="AN5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F6">
         <v>2019</v>
       </c>
       <c r="J6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="AN6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F7">
         <v>2019</v>
       </c>
       <c r="J7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="AN7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E8" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F8">
         <v>2017</v>
       </c>
       <c r="J8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="AN8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F9">
         <v>2016</v>
       </c>
       <c r="J9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AN9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F10">
         <v>2018</v>
       </c>
       <c r="J10" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="AN10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" t="s">
         <v>83</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11">
+        <v>2019</v>
+      </c>
+      <c r="J11" t="s">
+        <v>81</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:40" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" t="s">
         <v>84</v>
-      </c>
-      <c r="E11" t="s">
-        <v>82</v>
-      </c>
-      <c r="F11">
-        <v>2018</v>
-      </c>
-      <c r="J11" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="C12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E12" t="s">
-        <v>86</v>
       </c>
       <c r="F12">
         <v>2019</v>
       </c>
-      <c r="J12" t="s">
-        <v>87</v>
+      <c r="J12" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="AN12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:40" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F13">
-        <v>2019</v>
-      </c>
-      <c r="J13" s="2" t="s">
+        <v>2016</v>
+      </c>
+      <c r="J13" t="s">
         <v>91</v>
       </c>
       <c r="AN13" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:40" x14ac:dyDescent="0.2">
@@ -1725,44 +1664,44 @@
         <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="E14" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F14">
         <v>2013</v>
       </c>
       <c r="J14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN14" t="s">
         <v>41</v>
-      </c>
-      <c r="AN14" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C15" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" t="s">
         <v>98</v>
-      </c>
-      <c r="D15" t="s">
-        <v>97</v>
       </c>
       <c r="E15" t="s">
         <v>96</v>
       </c>
       <c r="F15">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="J15" t="s">
         <v>99</v>
       </c>
       <c r="AN15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C16" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
         <v>102</v>
@@ -1771,13 +1710,13 @@
         <v>100</v>
       </c>
       <c r="F16">
-        <v>2013</v>
-      </c>
-      <c r="J16" t="s">
-        <v>101</v>
+        <v>2017</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="AN16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="3:40" x14ac:dyDescent="0.2">
@@ -1791,38 +1730,38 @@
         <v>104</v>
       </c>
       <c r="F17">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="J17" t="s">
         <v>107</v>
       </c>
       <c r="AN17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="3:40" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C18" t="s">
         <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E18" t="s">
         <v>108</v>
       </c>
       <c r="F18">
-        <v>2017</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>111</v>
+        <v>2021</v>
+      </c>
+      <c r="J18" t="s">
+        <v>110</v>
       </c>
       <c r="AN18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="3:40" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C19" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D19" t="s">
         <v>114</v>
@@ -1831,13 +1770,13 @@
         <v>112</v>
       </c>
       <c r="F19">
-        <v>2018</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>115</v>
+        <v>2013</v>
+      </c>
+      <c r="J19" t="s">
+        <v>113</v>
       </c>
       <c r="AN19" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="3:40" x14ac:dyDescent="0.2">
@@ -1851,56 +1790,56 @@
         <v>116</v>
       </c>
       <c r="F20">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="J20" t="s">
         <v>119</v>
       </c>
       <c r="AN20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C21" t="s">
+        <v>122</v>
+      </c>
+      <c r="D21" t="s">
         <v>121</v>
-      </c>
-      <c r="D21" t="s">
-        <v>123</v>
       </c>
       <c r="E21" t="s">
         <v>120</v>
       </c>
       <c r="F21">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="J21" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AN21" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C22" t="s">
+        <v>126</v>
+      </c>
+      <c r="D22" t="s">
         <v>127</v>
-      </c>
-      <c r="D22" t="s">
-        <v>126</v>
       </c>
       <c r="E22" t="s">
         <v>124</v>
       </c>
       <c r="F22">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="J22" t="s">
         <v>125</v>
       </c>
       <c r="AN22" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="3:40" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C23" t="s">
         <v>129</v>
       </c>
@@ -1911,33 +1850,33 @@
         <v>128</v>
       </c>
       <c r="F23">
-        <v>2013</v>
-      </c>
-      <c r="J23" t="s">
+        <v>2020</v>
+      </c>
+      <c r="J23" s="2" t="s">
         <v>131</v>
       </c>
       <c r="AN23" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C24" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" t="s">
         <v>134</v>
-      </c>
-      <c r="D24" t="s">
-        <v>133</v>
       </c>
       <c r="E24" t="s">
         <v>132</v>
       </c>
       <c r="F24">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="J24" t="s">
         <v>135</v>
       </c>
       <c r="AN24" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="3:40" x14ac:dyDescent="0.2">
@@ -1945,27 +1884,27 @@
         <v>138</v>
       </c>
       <c r="D25" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E25" t="s">
         <v>136</v>
       </c>
       <c r="F25">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="J25" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AN25" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="26" spans="3:40" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C26" t="s">
+        <v>142</v>
+      </c>
+      <c r="D26" t="s">
         <v>141</v>
-      </c>
-      <c r="D26" t="s">
-        <v>142</v>
       </c>
       <c r="E26" t="s">
         <v>140</v>
@@ -1973,11 +1912,11 @@
       <c r="F26">
         <v>2020</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="J26" t="s">
         <v>143</v>
       </c>
       <c r="AN26" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="3:40" x14ac:dyDescent="0.2">
@@ -1991,53 +1930,53 @@
         <v>144</v>
       </c>
       <c r="F27">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="J27" t="s">
         <v>147</v>
       </c>
       <c r="AN27" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="3:40" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C28" t="s">
+        <v>149</v>
+      </c>
+      <c r="D28" t="s">
         <v>150</v>
-      </c>
-      <c r="D28" t="s">
-        <v>149</v>
       </c>
       <c r="E28" t="s">
         <v>148</v>
       </c>
       <c r="F28">
-        <v>2019</v>
-      </c>
-      <c r="J28" t="s">
+        <v>2018</v>
+      </c>
+      <c r="J28" s="2" t="s">
         <v>151</v>
       </c>
       <c r="AN28" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D29" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E29" t="s">
         <v>152</v>
       </c>
       <c r="F29">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="J29" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AN29" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="3:40" x14ac:dyDescent="0.2">
@@ -2045,179 +1984,179 @@
         <v>157</v>
       </c>
       <c r="D30" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E30" t="s">
         <v>156</v>
       </c>
       <c r="F30">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="J30" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AN30" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" spans="3:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C31" t="s">
+        <v>161</v>
+      </c>
+      <c r="D31" t="s">
+        <v>163</v>
+      </c>
+      <c r="E31" t="s">
         <v>160</v>
       </c>
-      <c r="D31" t="s">
+      <c r="F31">
+        <v>2017</v>
+      </c>
+      <c r="J31" t="s">
         <v>162</v>
       </c>
-      <c r="E31" t="s">
-        <v>40</v>
-      </c>
-      <c r="F31">
-        <v>2019</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>161</v>
-      </c>
       <c r="AN31" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="32" spans="3:40" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C32" t="s">
+        <v>165</v>
+      </c>
+      <c r="D32" t="s">
+        <v>166</v>
+      </c>
+      <c r="E32" t="s">
         <v>164</v>
-      </c>
-      <c r="D32" t="s">
-        <v>165</v>
-      </c>
-      <c r="E32" t="s">
-        <v>163</v>
       </c>
       <c r="F32">
         <v>2018</v>
       </c>
-      <c r="J32" s="2" t="s">
-        <v>166</v>
+      <c r="J32" t="s">
+        <v>167</v>
       </c>
       <c r="AN32" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C33" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D33" t="s">
         <v>170</v>
       </c>
       <c r="E33" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F33">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="J33" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AN33" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C34" t="s">
+        <v>173</v>
+      </c>
+      <c r="D34" t="s">
+        <v>175</v>
+      </c>
+      <c r="E34" t="s">
         <v>172</v>
       </c>
-      <c r="D34" t="s">
+      <c r="F34">
+        <v>2017</v>
+      </c>
+      <c r="J34" t="s">
         <v>174</v>
       </c>
-      <c r="E34" t="s">
-        <v>171</v>
-      </c>
-      <c r="F34">
-        <v>2016</v>
-      </c>
-      <c r="J34" t="s">
-        <v>173</v>
-      </c>
       <c r="AN34" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C35" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D35" t="s">
         <v>178</v>
       </c>
       <c r="E35" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F35">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="J35" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AN35" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C36" t="s">
+        <v>181</v>
+      </c>
+      <c r="D36" t="s">
+        <v>182</v>
+      </c>
+      <c r="E36" t="s">
         <v>180</v>
       </c>
-      <c r="D36" t="s">
-        <v>181</v>
-      </c>
-      <c r="E36" t="s">
-        <v>179</v>
-      </c>
       <c r="F36">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="J36" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AN36" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C37" t="s">
+        <v>185</v>
+      </c>
+      <c r="D37" t="s">
+        <v>186</v>
+      </c>
+      <c r="E37" t="s">
         <v>184</v>
       </c>
-      <c r="D37" t="s">
-        <v>185</v>
-      </c>
-      <c r="E37" t="s">
-        <v>183</v>
-      </c>
       <c r="F37">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="J37" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AN37" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="38" spans="3:40" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="3:40" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C38" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D38" t="s">
         <v>190</v>
       </c>
       <c r="E38" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F38">
-        <v>2017</v>
-      </c>
-      <c r="J38" t="s">
-        <v>189</v>
+        <v>2023</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>191</v>
       </c>
       <c r="AN38" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39" spans="3:40" x14ac:dyDescent="0.2">
@@ -2225,182 +2164,179 @@
         <v>192</v>
       </c>
       <c r="D39" t="s">
+        <v>194</v>
+      </c>
+      <c r="E39" t="s">
         <v>193</v>
-      </c>
-      <c r="E39" t="s">
-        <v>191</v>
       </c>
       <c r="F39">
         <v>2014</v>
       </c>
       <c r="J39" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AN39" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C40" t="s">
+        <v>197</v>
+      </c>
+      <c r="D40" t="s">
+        <v>198</v>
+      </c>
+      <c r="E40" t="s">
         <v>196</v>
       </c>
-      <c r="D40" t="s">
-        <v>197</v>
-      </c>
-      <c r="E40" t="s">
-        <v>195</v>
-      </c>
       <c r="F40">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="J40" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AN40" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C41" t="s">
+        <v>201</v>
+      </c>
+      <c r="D41" t="s">
+        <v>202</v>
+      </c>
+      <c r="E41" t="s">
         <v>200</v>
       </c>
-      <c r="D41" t="s">
-        <v>201</v>
-      </c>
-      <c r="E41" t="s">
-        <v>199</v>
-      </c>
       <c r="F41">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="J41" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AN41" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="42" spans="3:40" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C42" t="s">
+        <v>205</v>
+      </c>
+      <c r="D42" t="s">
+        <v>207</v>
+      </c>
+      <c r="E42" t="s">
         <v>204</v>
       </c>
-      <c r="D42" t="s">
-        <v>205</v>
-      </c>
-      <c r="E42" t="s">
-        <v>203</v>
-      </c>
       <c r="F42">
-        <v>2023</v>
-      </c>
-      <c r="J42" s="2" t="s">
+        <v>2021</v>
+      </c>
+      <c r="J42" t="s">
         <v>206</v>
       </c>
       <c r="AN42" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C43" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D43" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E43" t="s">
         <v>208</v>
       </c>
       <c r="F43">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="J43" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AN43" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C44" t="s">
+        <v>213</v>
+      </c>
+      <c r="D44" t="s">
+        <v>214</v>
+      </c>
+      <c r="E44" t="s">
         <v>212</v>
       </c>
-      <c r="D44" t="s">
-        <v>213</v>
-      </c>
-      <c r="E44" t="s">
-        <v>211</v>
-      </c>
       <c r="F44">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="J44" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AN44" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C45" t="s">
+        <v>217</v>
+      </c>
+      <c r="D45" t="s">
+        <v>218</v>
+      </c>
+      <c r="E45" t="s">
         <v>216</v>
       </c>
-      <c r="D45" t="s">
-        <v>217</v>
-      </c>
-      <c r="E45" t="s">
-        <v>215</v>
-      </c>
       <c r="F45">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="J45" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AN45" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C46" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D46" t="s">
         <v>222</v>
       </c>
       <c r="E46" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F46">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="J46" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AN46" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C47" t="s">
+        <v>226</v>
+      </c>
+      <c r="D47" t="s">
+        <v>127</v>
+      </c>
+      <c r="E47" t="s">
+        <v>224</v>
+      </c>
+      <c r="J47" t="s">
         <v>225</v>
       </c>
-      <c r="D47" t="s">
-        <v>226</v>
-      </c>
-      <c r="E47" t="s">
-        <v>223</v>
-      </c>
-      <c r="F47">
-        <v>2024</v>
-      </c>
-      <c r="J47" t="s">
-        <v>224</v>
-      </c>
       <c r="AN47" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="48" spans="3:40" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" spans="3:40" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C48" t="s">
         <v>228</v>
       </c>
@@ -2411,13 +2347,13 @@
         <v>227</v>
       </c>
       <c r="F48">
-        <v>2022</v>
-      </c>
-      <c r="J48" t="s">
+        <v>2016</v>
+      </c>
+      <c r="J48" s="2" t="s">
         <v>230</v>
       </c>
       <c r="AN48" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="3:40" x14ac:dyDescent="0.2">
@@ -2425,19 +2361,19 @@
         <v>232</v>
       </c>
       <c r="D49" t="s">
-        <v>233</v>
+        <v>127</v>
       </c>
       <c r="E49" t="s">
         <v>231</v>
       </c>
       <c r="F49">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="J49" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AN49" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="50" spans="3:40" x14ac:dyDescent="0.2">
@@ -2445,76 +2381,79 @@
         <v>236</v>
       </c>
       <c r="D50" t="s">
-        <v>237</v>
+        <v>127</v>
       </c>
       <c r="E50" t="s">
+        <v>234</v>
+      </c>
+      <c r="F50">
+        <v>2022</v>
+      </c>
+      <c r="J50" t="s">
         <v>235</v>
       </c>
-      <c r="F50">
-        <v>2020</v>
-      </c>
-      <c r="J50" t="s">
-        <v>238</v>
-      </c>
       <c r="AN50" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C51" t="s">
+        <v>238</v>
+      </c>
+      <c r="D51" t="s">
+        <v>240</v>
+      </c>
+      <c r="E51" t="s">
+        <v>237</v>
+      </c>
+      <c r="F51">
+        <v>2024</v>
+      </c>
+      <c r="J51" t="s">
+        <v>239</v>
+      </c>
+      <c r="AN51" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="C52" t="s">
+        <v>244</v>
+      </c>
+      <c r="D52" t="s">
+        <v>242</v>
+      </c>
+      <c r="E52" t="s">
         <v>241</v>
       </c>
-      <c r="D51" t="s">
-        <v>139</v>
-      </c>
-      <c r="E51" t="s">
-        <v>239</v>
-      </c>
-      <c r="J51" t="s">
-        <v>240</v>
-      </c>
-      <c r="AN51" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="52" spans="3:40" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C52" t="s">
+      <c r="F52">
+        <v>2015</v>
+      </c>
+      <c r="J52" t="s">
         <v>243</v>
       </c>
-      <c r="D52" t="s">
-        <v>244</v>
-      </c>
-      <c r="E52" t="s">
-        <v>242</v>
-      </c>
-      <c r="F52">
-        <v>2016</v>
-      </c>
-      <c r="J52" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="AN52" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C53" t="s">
+        <v>246</v>
+      </c>
+      <c r="D53" t="s">
+        <v>248</v>
+      </c>
+      <c r="E53" t="s">
+        <v>245</v>
+      </c>
+      <c r="F53">
+        <v>2018</v>
+      </c>
+      <c r="J53" t="s">
         <v>247</v>
       </c>
-      <c r="D53" t="s">
-        <v>139</v>
-      </c>
-      <c r="E53" t="s">
-        <v>246</v>
-      </c>
-      <c r="F53">
-        <v>2022</v>
-      </c>
-      <c r="J53" t="s">
-        <v>248</v>
-      </c>
       <c r="AN53" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54" spans="3:40" x14ac:dyDescent="0.2">
@@ -2522,19 +2461,19 @@
         <v>251</v>
       </c>
       <c r="D54" t="s">
-        <v>139</v>
+        <v>89</v>
       </c>
       <c r="E54" t="s">
         <v>249</v>
       </c>
       <c r="F54">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="J54" t="s">
         <v>250</v>
       </c>
       <c r="AN54" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55" spans="3:40" x14ac:dyDescent="0.2">
@@ -2548,21 +2487,21 @@
         <v>252</v>
       </c>
       <c r="F55">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="J55" t="s">
         <v>254</v>
       </c>
       <c r="AN55" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="56" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C56" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D56" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E56" t="s">
         <v>256</v>
@@ -2571,10 +2510,10 @@
         <v>2015</v>
       </c>
       <c r="J56" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AN56" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57" spans="3:40" x14ac:dyDescent="0.2">
@@ -2582,27 +2521,27 @@
         <v>261</v>
       </c>
       <c r="D57" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E57" t="s">
         <v>260</v>
       </c>
       <c r="F57">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="J57" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AN57" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="58" spans="3:40" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C58" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D58" t="s">
-        <v>97</v>
+        <v>229</v>
       </c>
       <c r="E58" t="s">
         <v>264</v>
@@ -2610,31 +2549,31 @@
       <c r="F58">
         <v>2016</v>
       </c>
-      <c r="J58" t="s">
-        <v>265</v>
+      <c r="J58" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="AN58" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="59" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C59" t="s">
+        <v>269</v>
+      </c>
+      <c r="D59" t="s">
         <v>268</v>
-      </c>
-      <c r="D59" t="s">
-        <v>270</v>
       </c>
       <c r="E59" t="s">
         <v>267</v>
       </c>
       <c r="F59">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="J59" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN59" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="60" spans="3:40" x14ac:dyDescent="0.2">
@@ -2642,159 +2581,79 @@
         <v>272</v>
       </c>
       <c r="D60" t="s">
-        <v>273</v>
+        <v>40</v>
       </c>
       <c r="E60" t="s">
         <v>271</v>
       </c>
       <c r="F60">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="J60" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AN60" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="61" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C61" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D61" t="s">
-        <v>277</v>
+        <v>127</v>
       </c>
       <c r="E61" t="s">
         <v>275</v>
       </c>
       <c r="F61">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="J61" t="s">
+        <v>276</v>
+      </c>
+      <c r="AN61" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="62" spans="3:40" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C62" t="s">
+        <v>277</v>
+      </c>
+      <c r="D62" t="s">
         <v>278</v>
-      </c>
-      <c r="AN61" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="62" spans="3:40" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C62" t="s">
-        <v>280</v>
-      </c>
-      <c r="D62" t="s">
-        <v>244</v>
       </c>
       <c r="E62" t="s">
         <v>279</v>
       </c>
       <c r="F62">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="J62" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="AN62" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="63" spans="3:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C63" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="AN62" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
-      <c r="C63" t="s">
-        <v>284</v>
-      </c>
       <c r="D63" t="s">
-        <v>283</v>
+        <v>40</v>
       </c>
       <c r="E63" t="s">
         <v>282</v>
       </c>
       <c r="F63">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="J63" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AN63" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
-      <c r="C64" t="s">
-        <v>287</v>
-      </c>
-      <c r="D64" t="s">
-        <v>43</v>
-      </c>
-      <c r="E64" t="s">
-        <v>286</v>
-      </c>
-      <c r="F64">
-        <v>2021</v>
-      </c>
-      <c r="J64" t="s">
-        <v>288</v>
-      </c>
-      <c r="AN64" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="65" spans="3:40" x14ac:dyDescent="0.2">
-      <c r="C65" t="s">
-        <v>289</v>
-      </c>
-      <c r="D65" t="s">
-        <v>139</v>
-      </c>
-      <c r="E65" t="s">
-        <v>290</v>
-      </c>
-      <c r="F65">
-        <v>2024</v>
-      </c>
-      <c r="J65" t="s">
-        <v>291</v>
-      </c>
-      <c r="AN65" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="66" spans="3:40" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C66" t="s">
-        <v>292</v>
-      </c>
-      <c r="D66" t="s">
-        <v>293</v>
-      </c>
-      <c r="E66" t="s">
-        <v>294</v>
-      </c>
-      <c r="F66">
-        <v>2020</v>
-      </c>
-      <c r="J66" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="AN66" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="67" spans="3:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C67" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="D67" t="s">
-        <v>43</v>
-      </c>
-      <c r="E67" t="s">
-        <v>297</v>
-      </c>
-      <c r="F67">
-        <v>2015</v>
-      </c>
-      <c r="J67" t="s">
-        <v>298</v>
-      </c>
-      <c r="AN67" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -2803,6 +2662,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B6889C2593FACB4192549183B8B19287" ma:contentTypeVersion="11" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="8f919e2780f892880bff7efb43d3db1d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ab92c565-5003-4ac3-93a3-a3ce8796a3c0" xmlns:ns3="aa1b21cb-23df-461b-8b8e-4aaeac2f3f50" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1ca4d89da73e1329ebe7ff2e4ed471c6" ns2:_="" ns3:_="">
     <xsd:import namespace="ab92c565-5003-4ac3-93a3-a3ce8796a3c0"/>
@@ -2997,15 +2865,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3018,13 +2877,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94938947-D3FB-4C4F-AC3A-8ADD833FB410}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76A91DD2-672F-4BCE-B66C-C5F5DA651FB3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76A91DD2-672F-4BCE-B66C-C5F5DA651FB3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94938947-D3FB-4C4F-AC3A-8ADD833FB410}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="ab92c565-5003-4ac3-93a3-a3ce8796a3c0"/>
+    <ds:schemaRef ds:uri="aa1b21cb-23df-461b-8b8e-4aaeac2f3f50"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3677C3C-B56C-4706-8251-166ABA5ABBE9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3677C3C-B56C-4706-8251-166ABA5ABBE9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ab92c565-5003-4ac3-93a3-a3ce8796a3c0"/>
+    <ds:schemaRef ds:uri="aa1b21cb-23df-461b-8b8e-4aaeac2f3f50"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>